--- a/jogos_2025-07-03.xlsx
+++ b/jogos_2025-07-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="95">
   <si>
     <t>Date</t>
   </si>
@@ -193,9 +193,6 @@
     <t>16:15</t>
   </si>
   <si>
-    <t>19:00</t>
-  </si>
-  <si>
     <t>20:00</t>
   </si>
   <si>
@@ -211,48 +208,45 @@
     <t>23:00</t>
   </si>
   <si>
+    <t>Uzbekistan Uzbekistan Super League</t>
+  </si>
+  <si>
     <t>Belarus Vysheyshaya Liga</t>
   </si>
   <si>
-    <t>Uzbekistan Uzbekistan Super League</t>
-  </si>
-  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
+    <t>USA USL Championship</t>
+  </si>
+  <si>
+    <t>USA MLS</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>USA USL Championship</t>
-  </si>
-  <si>
-    <t>USA MLS</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
     <t>2025</t>
   </si>
   <si>
+    <t>Shortan</t>
+  </si>
+  <si>
     <t>MKK-Dnepr</t>
   </si>
   <si>
-    <t>Shortan</t>
-  </si>
-  <si>
     <t>Víkingur</t>
   </si>
   <si>
     <t>Afturelding</t>
   </si>
   <si>
-    <t>Goiás</t>
-  </si>
-  <si>
     <t>Loudoun United</t>
   </si>
   <si>
@@ -271,19 +265,16 @@
     <t>Tacoma Defiance</t>
   </si>
   <si>
+    <t>Qizilqum</t>
+  </si>
+  <si>
     <t>Dinamo Minsk</t>
   </si>
   <si>
-    <t>Qizilqum</t>
-  </si>
-  <si>
     <t>KÍ</t>
   </si>
   <si>
     <t>Breidablik</t>
-  </si>
-  <si>
-    <t>Criciúma</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -671,7 +662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD12"/>
+  <dimension ref="A1:BD11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:56">
@@ -852,16 +843,16 @@
         <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" t="s">
         <v>73</v>
       </c>
-      <c r="E2" t="s">
-        <v>74</v>
-      </c>
       <c r="F2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -876,16 +867,16 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L2">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -927,10 +918,10 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC2">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -951,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AK2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1022,16 +1013,16 @@
         <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1046,16 +1037,16 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -1097,10 +1088,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -1121,10 +1112,10 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AK3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1192,16 +1183,16 @@
         <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1216,16 +1207,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -1237,73 +1228,73 @@
         <v>0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AK4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AM4">
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO4">
         <v>-1</v>
@@ -1362,16 +1353,16 @@
         <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1386,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L5">
         <v>4.1</v>
@@ -1407,34 +1398,34 @@
         <v>1.57</v>
       </c>
       <c r="R5">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S5">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="T5">
         <v>2.2</v>
       </c>
       <c r="U5">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="W5">
+        <v>1.14</v>
+      </c>
+      <c r="X5">
+        <v>1.03</v>
+      </c>
+      <c r="Y5">
+        <v>15</v>
+      </c>
+      <c r="Z5">
         <v>1.17</v>
       </c>
-      <c r="X5">
-        <v>1.02</v>
-      </c>
-      <c r="Y5">
-        <v>13.5</v>
-      </c>
-      <c r="Z5">
-        <v>1.16</v>
-      </c>
       <c r="AA5">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AB5">
         <v>1.5</v>
@@ -1449,22 +1440,22 @@
         <v>1.75</v>
       </c>
       <c r="AF5">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AG5">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AH5">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AI5">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AJ5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AK5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AL5">
         <v>1.25</v>
@@ -1473,7 +1464,7 @@
         <v>1.18</v>
       </c>
       <c r="AN5">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AO5">
         <v>-1</v>
@@ -1532,16 +1523,16 @@
         <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1556,16 +1547,16 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1613,10 +1604,10 @@
         <v>0</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF6">
         <v>0</v>
@@ -1631,10 +1622,10 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AK6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1691,7 +1682,7 @@
         <v>0</v>
       </c>
       <c r="BD6" s="3">
-        <v>45841.79166666666</v>
+        <v>45841.83333333334</v>
       </c>
     </row>
     <row r="7" spans="1:56">
@@ -1702,16 +1693,16 @@
         <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1726,127 +1717,127 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AK7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AO7">
         <v>-1</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AZ7">
         <v>0</v>
@@ -1855,13 +1846,13 @@
         <v>0</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BD7" s="3">
-        <v>45841.83333333334</v>
+        <v>45841.85416666666</v>
       </c>
     </row>
     <row r="8" spans="1:56">
@@ -1872,16 +1863,16 @@
         <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1896,94 +1887,94 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L8">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="M8">
-        <v>3.73</v>
+        <v>3.3</v>
       </c>
       <c r="N8">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="O8">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="P8">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="R8">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="S8">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="T8">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="U8">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="V8">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z8">
+        <v>1.36</v>
+      </c>
+      <c r="AA8">
+        <v>2.9</v>
+      </c>
+      <c r="AB8">
+        <v>1.92</v>
+      </c>
+      <c r="AC8">
+        <v>1.78</v>
+      </c>
+      <c r="AD8">
+        <v>3.7</v>
+      </c>
+      <c r="AE8">
         <v>1.22</v>
       </c>
-      <c r="AA8">
-        <v>3.8</v>
-      </c>
-      <c r="AB8">
-        <v>1.67</v>
-      </c>
-      <c r="AC8">
-        <v>2.05</v>
-      </c>
-      <c r="AD8">
-        <v>2.7</v>
-      </c>
-      <c r="AE8">
-        <v>1.4</v>
-      </c>
       <c r="AF8">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG8">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH8">
-        <v>4.75</v>
+        <v>7.5</v>
       </c>
       <c r="AI8">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AJ8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AK8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AL8">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AM8">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AN8">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AO8">
         <v>-1</v>
@@ -1992,31 +1983,31 @@
         <v>1.22</v>
       </c>
       <c r="AQ8">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR8">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AS8">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AT8">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="AU8">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AV8">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AW8">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AX8">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AY8">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AZ8">
         <v>0</v>
@@ -2025,13 +2016,13 @@
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="BC8">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="BD8" s="3">
-        <v>45841.85416666666</v>
+        <v>45841.89930555555</v>
       </c>
     </row>
     <row r="9" spans="1:56">
@@ -2042,16 +2033,16 @@
         <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2066,16 +2057,16 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L9">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -2117,10 +2108,10 @@
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD9">
         <v>0</v>
@@ -2141,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AK9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2201,7 +2192,7 @@
         <v>0</v>
       </c>
       <c r="BD9" s="3">
-        <v>45841.89930555555</v>
+        <v>45841.90625</v>
       </c>
     </row>
     <row r="10" spans="1:56">
@@ -2212,32 +2203,32 @@
         <v>63</v>
       </c>
       <c r="C10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" t="s">
         <v>72</v>
       </c>
-      <c r="D10" t="s">
-        <v>73</v>
-      </c>
       <c r="E10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
         <v>93</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" t="s">
-        <v>96</v>
-      </c>
       <c r="L10">
         <v>0</v>
       </c>
@@ -2311,10 +2302,10 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AK10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2371,7 +2362,7 @@
         <v>0</v>
       </c>
       <c r="BD10" s="3">
-        <v>45841.90625</v>
+        <v>45841.95833333334</v>
       </c>
     </row>
     <row r="11" spans="1:56">
@@ -2379,112 +2370,112 @@
         <v>45841</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" t="s">
         <v>72</v>
       </c>
-      <c r="D11" t="s">
-        <v>73</v>
-      </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F11" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
+        <v>93</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="s">
         <v>94</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" t="s">
-        <v>96</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <v>0</v>
-      </c>
-      <c r="X11">
-        <v>0</v>
-      </c>
-      <c r="Y11">
-        <v>0</v>
-      </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0</v>
-      </c>
-      <c r="AC11">
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>0</v>
-      </c>
-      <c r="AG11">
-        <v>0</v>
-      </c>
-      <c r="AH11">
-        <v>0</v>
-      </c>
-      <c r="AI11">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>97</v>
-      </c>
       <c r="AK11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2541,176 +2532,6 @@
         <v>0</v>
       </c>
       <c r="BD11" s="3">
-        <v>45841.95833333334</v>
-      </c>
-    </row>
-    <row r="12" spans="1:56">
-      <c r="A12" s="2">
-        <v>45841</v>
-      </c>
-      <c r="B12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" t="s">
-        <v>84</v>
-      </c>
-      <c r="F12" t="s">
-        <v>95</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" t="s">
-        <v>96</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>0</v>
-      </c>
-      <c r="Y12">
-        <v>0</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
-      <c r="AC12">
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>0</v>
-      </c>
-      <c r="AG12">
-        <v>0</v>
-      </c>
-      <c r="AH12">
-        <v>0</v>
-      </c>
-      <c r="AI12">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>97</v>
-      </c>
-      <c r="AK12" t="s">
-        <v>97</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>0</v>
-      </c>
-      <c r="AO12">
-        <v>-1</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12">
-        <v>0</v>
-      </c>
-      <c r="AV12">
-        <v>0</v>
-      </c>
-      <c r="AW12">
-        <v>0</v>
-      </c>
-      <c r="AX12">
-        <v>0</v>
-      </c>
-      <c r="AY12">
-        <v>0</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>0</v>
-      </c>
-      <c r="BC12">
-        <v>0</v>
-      </c>
-      <c r="BD12" s="3">
         <v>45841.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-07-03.xlsx
+++ b/jogos_2025-07-03.xlsx
@@ -208,12 +208,12 @@
     <t>23:00</t>
   </si>
   <si>
+    <t>Belarus Vysheyshaya Liga</t>
+  </si>
+  <si>
     <t>Uzbekistan Uzbekistan Super League</t>
   </si>
   <si>
-    <t>Belarus Vysheyshaya Liga</t>
-  </si>
-  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
@@ -235,12 +235,12 @@
     <t>2025</t>
   </si>
   <si>
+    <t>MKK-Dnepr</t>
+  </si>
+  <si>
     <t>Shortan</t>
   </si>
   <si>
-    <t>MKK-Dnepr</t>
-  </si>
-  <si>
     <t>Víkingur</t>
   </si>
   <si>
@@ -259,18 +259,18 @@
     <t>North Texas</t>
   </si>
   <si>
+    <t>Tacoma Defiance</t>
+  </si>
+  <si>
     <t>LA Galaxy II</t>
   </si>
   <si>
-    <t>Tacoma Defiance</t>
+    <t>Dinamo Minsk</t>
   </si>
   <si>
     <t>Qizilqum</t>
   </si>
   <si>
-    <t>Dinamo Minsk</t>
-  </si>
-  <si>
     <t>KÍ</t>
   </si>
   <si>
@@ -289,10 +289,10 @@
     <t>Minnesota United II</t>
   </si>
   <si>
+    <t>San Jose Earthquakes II</t>
+  </si>
+  <si>
     <t>Whitecaps II</t>
-  </si>
-  <si>
-    <t>San Jose Earthquakes II</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -870,13 +870,13 @@
         <v>93</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -918,10 +918,10 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -1040,13 +1040,13 @@
         <v>93</v>
       </c>
       <c r="L3">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -1088,10 +1088,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC3">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -1219,43 +1219,43 @@
         <v>1.88</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>12.75</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R4">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="S4">
-        <v>2.85</v>
+        <v>3.34</v>
       </c>
       <c r="T4">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="U4">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="V4">
-        <v>5.75</v>
+        <v>4.9</v>
       </c>
       <c r="W4">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z4">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AA4">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AB4">
         <v>1.75</v>
@@ -1264,22 +1264,22 @@
         <v>1.97</v>
       </c>
       <c r="AD4">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="AE4">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AF4">
         <v>1.62</v>
       </c>
       <c r="AG4">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH4">
-        <v>4.9</v>
+        <v>4.15</v>
       </c>
       <c r="AI4">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AJ4" t="s">
         <v>94</v>
@@ -1288,13 +1288,13 @@
         <v>94</v>
       </c>
       <c r="AL4">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN4">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AO4">
         <v>-1</v>
@@ -1336,10 +1336,10 @@
         <v>0</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BD4" s="3">
         <v>45841.625</v>
@@ -1380,13 +1380,13 @@
         <v>93</v>
       </c>
       <c r="L5">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="M5">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="N5">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="O5">
         <v>2.5</v>
@@ -1398,7 +1398,7 @@
         <v>1.57</v>
       </c>
       <c r="R5">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="S5">
         <v>3.3</v>
@@ -1422,10 +1422,10 @@
         <v>15</v>
       </c>
       <c r="Z5">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AA5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AB5">
         <v>1.5</v>
@@ -1443,10 +1443,10 @@
         <v>1.52</v>
       </c>
       <c r="AG5">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AI5">
         <v>1.22</v>
@@ -1470,34 +1470,34 @@
         <v>-1</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AZ5">
         <v>0</v>
@@ -1559,49 +1559,49 @@
         <v>3.55</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD6">
         <v>2.17</v>
@@ -1610,16 +1610,16 @@
         <v>1.62</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ6" t="s">
         <v>94</v>
@@ -1628,13 +1628,13 @@
         <v>94</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AM6">
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO6">
         <v>-1</v>
@@ -1676,10 +1676,10 @@
         <v>0</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BD6" s="3">
         <v>45841.83333333334</v>
@@ -1908,25 +1908,25 @@
         <v>2.65</v>
       </c>
       <c r="R8">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="S8">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="T8">
-        <v>3.1</v>
+        <v>3.33</v>
       </c>
       <c r="U8">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V8">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="W8">
         <v>1.06</v>
       </c>
       <c r="X8">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y8">
         <v>8</v>
@@ -1944,7 +1944,7 @@
         <v>1.78</v>
       </c>
       <c r="AD8">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AE8">
         <v>1.22</v>
@@ -1956,7 +1956,7 @@
         <v>1.85</v>
       </c>
       <c r="AH8">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="AI8">
         <v>1.06</v>
@@ -1980,34 +1980,34 @@
         <v>-1</v>
       </c>
       <c r="AP8">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ8">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR8">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AS8">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AT8">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="AU8">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AV8">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AW8">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AX8">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AY8">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AZ8">
         <v>0</v>
@@ -2060,40 +2060,40 @@
         <v>93</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X9">
         <v>0</v>
@@ -2102,34 +2102,34 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ9" t="s">
         <v>94</v>
@@ -2138,13 +2138,13 @@
         <v>94</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AM9">
         <v>0</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO9">
         <v>-1</v>
@@ -2186,10 +2186,10 @@
         <v>0</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD9" s="3">
         <v>45841.90625</v>
@@ -2230,22 +2230,22 @@
         <v>93</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2254,10 +2254,10 @@
         <v>0</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V10">
         <v>0</v>
@@ -2278,28 +2278,28 @@
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AJ10" t="s">
         <v>94</v>
@@ -2308,13 +2308,13 @@
         <v>94</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AM10">
         <v>0</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AO10">
         <v>-1</v>
@@ -2356,10 +2356,10 @@
         <v>0</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD10" s="3">
         <v>45841.95833333334</v>
@@ -2418,22 +2418,22 @@
         <v>0</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X11">
         <v>0</v>
@@ -2442,34 +2442,34 @@
         <v>0</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AJ11" t="s">
         <v>94</v>
@@ -2478,13 +2478,13 @@
         <v>94</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AM11">
         <v>0</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AO11">
         <v>-1</v>

--- a/jogos_2025-07-03.xlsx
+++ b/jogos_2025-07-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -208,12 +154,12 @@
     <t>23:00</t>
   </si>
   <si>
+    <t>Uzbekistan Uzbekistan Super League</t>
+  </si>
+  <si>
     <t>Belarus Vysheyshaya Liga</t>
   </si>
   <si>
-    <t>Uzbekistan Uzbekistan Super League</t>
-  </si>
-  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
@@ -235,12 +181,12 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Shortan</t>
+  </si>
+  <si>
     <t>MKK-Dnepr</t>
   </si>
   <si>
-    <t>Shortan</t>
-  </si>
-  <si>
     <t>Víkingur</t>
   </si>
   <si>
@@ -265,12 +211,12 @@
     <t>LA Galaxy II</t>
   </si>
   <si>
+    <t>Qizilqum</t>
+  </si>
+  <si>
     <t>Dinamo Minsk</t>
   </si>
   <si>
-    <t>Qizilqum</t>
-  </si>
-  <si>
     <t>KÍ</t>
   </si>
   <si>
@@ -295,10 +241,55 @@
     <t>Whitecaps II</t>
   </si>
   <si>
-    <t>incomplete</t>
+    <t>complete</t>
+  </si>
+  <si>
+    <t>['45+2']</t>
+  </si>
+  <si>
+    <t>['12', '18']</t>
   </si>
   <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['44', '47']</t>
+  </si>
+  <si>
+    <t>['20', '49', '74']</t>
+  </si>
+  <si>
+    <t>['14', '61']</t>
+  </si>
+  <si>
+    <t>['2', '46', '54']</t>
+  </si>
+  <si>
+    <t>['43', '59', '6', '90+6']</t>
+  </si>
+  <si>
+    <t>['63']</t>
+  </si>
+  <si>
+    <t>['42', '69']</t>
+  </si>
+  <si>
+    <t>['64']</t>
+  </si>
+  <si>
+    <t>['7', '37']</t>
+  </si>
+  <si>
+    <t>['6']</t>
+  </si>
+  <si>
+    <t>['86']</t>
+  </si>
+  <si>
+    <t>['53', '27', '85', '90+1']</t>
+  </si>
+  <si>
+    <t>['18', '45']</t>
   </si>
 </sst>
 </file>
@@ -662,10 +653,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD11"/>
+  <dimension ref="A1:AL11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -780,273 +771,165 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45841</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="F2" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="L2">
-        <v>2.25</v>
+        <v>2.58</v>
       </c>
       <c r="M2">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N2">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AB2">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AC2">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ2" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AK2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>0</v>
-      </c>
-      <c r="AO2">
-        <v>-1</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
-      </c>
-      <c r="AU2">
-        <v>0</v>
-      </c>
-      <c r="AV2">
-        <v>0</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2">
-        <v>0</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>0</v>
-      </c>
-      <c r="BC2">
-        <v>0</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>85</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45841.5</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45841</v>
       </c>
       <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" t="s">
         <v>56</v>
       </c>
-      <c r="C3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E3" t="s">
-        <v>74</v>
-      </c>
       <c r="F3" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -1082,16 +965,16 @@
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -1112,111 +995,57 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AK3" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AO3">
-        <v>-1</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>0</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
-      </c>
-      <c r="AW3">
-        <v>0</v>
-      </c>
-      <c r="AX3">
-        <v>0</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>0</v>
-      </c>
-      <c r="BC3">
-        <v>0</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>78</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45841.5</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45841</v>
       </c>
       <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" t="s">
         <v>57</v>
       </c>
-      <c r="C4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
         <v>75</v>
       </c>
-      <c r="F4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" t="s">
-        <v>93</v>
-      </c>
       <c r="L4">
-        <v>3.45</v>
+        <v>4.93</v>
       </c>
       <c r="M4">
-        <v>3.55</v>
+        <v>3.78</v>
       </c>
       <c r="N4">
-        <v>1.88</v>
+        <v>1.51</v>
       </c>
       <c r="O4">
         <v>2.38</v>
@@ -1228,165 +1057,111 @@
         <v>1.62</v>
       </c>
       <c r="R4">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S4">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="T4">
         <v>2.3</v>
       </c>
       <c r="U4">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="V4">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="W4">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z4">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA4">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AB4">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC4">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AD4">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AE4">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AF4">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG4">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH4">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="AI4">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AJ4" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="AK4" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL4">
-        <v>1.25</v>
-      </c>
-      <c r="AM4">
-        <v>1.24</v>
-      </c>
-      <c r="AN4">
-        <v>1.18</v>
-      </c>
-      <c r="AO4">
-        <v>-1</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
-      </c>
-      <c r="AU4">
-        <v>0</v>
-      </c>
-      <c r="AV4">
-        <v>0</v>
-      </c>
-      <c r="AW4">
-        <v>0</v>
-      </c>
-      <c r="AX4">
-        <v>0</v>
-      </c>
-      <c r="AY4">
-        <v>0</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>2.38</v>
-      </c>
-      <c r="BC4">
-        <v>1.62</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>86</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45841.625</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45841</v>
       </c>
       <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" t="s">
         <v>58</v>
       </c>
-      <c r="C5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E5" t="s">
-        <v>76</v>
-      </c>
       <c r="F5" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="L5">
-        <v>3.7</v>
+        <v>3.97</v>
       </c>
       <c r="M5">
-        <v>3.88</v>
+        <v>4.1</v>
       </c>
       <c r="N5">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="O5">
         <v>2.5</v>
@@ -1398,141 +1173,87 @@
         <v>1.57</v>
       </c>
       <c r="R5">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S5">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T5">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="U5">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="V5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="W5">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X5">
         <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z5">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AA5">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AB5">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC5">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AD5">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AE5">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AF5">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG5">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH5">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AI5">
         <v>1.22</v>
       </c>
       <c r="AJ5" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="AK5" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL5">
-        <v>1.25</v>
-      </c>
-      <c r="AM5">
-        <v>1.18</v>
-      </c>
-      <c r="AN5">
-        <v>1.25</v>
-      </c>
-      <c r="AO5">
-        <v>-1</v>
-      </c>
-      <c r="AP5">
-        <v>1.11</v>
-      </c>
-      <c r="AQ5">
-        <v>1.16</v>
-      </c>
-      <c r="AR5">
-        <v>1.45</v>
-      </c>
-      <c r="AS5">
-        <v>1.65</v>
-      </c>
-      <c r="AT5">
-        <v>1.95</v>
-      </c>
-      <c r="AU5">
-        <v>5.5</v>
-      </c>
-      <c r="AV5">
-        <v>3.8</v>
-      </c>
-      <c r="AW5">
-        <v>2.8</v>
-      </c>
-      <c r="AX5">
-        <v>2.1</v>
-      </c>
-      <c r="AY5">
-        <v>1.75</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>2.5</v>
-      </c>
-      <c r="BC5">
-        <v>1.57</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>87</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45841.67708333334</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45841</v>
       </c>
       <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" t="s">
         <v>59</v>
       </c>
-      <c r="C6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" t="s">
-        <v>77</v>
-      </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1547,16 +1268,16 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="L6">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="M6">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="N6">
-        <v>3.55</v>
+        <v>4.06</v>
       </c>
       <c r="O6">
         <v>1.57</v>
@@ -1568,22 +1289,22 @@
         <v>2.38</v>
       </c>
       <c r="R6">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S6">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T6">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="U6">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="W6">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
         <v>1.02</v>
@@ -1592,132 +1313,78 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AA6">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AB6">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AC6">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AD6">
-        <v>2.17</v>
+        <v>2.75</v>
       </c>
       <c r="AE6">
+        <v>1.4</v>
+      </c>
+      <c r="AF6">
         <v>1.62</v>
       </c>
-      <c r="AF6">
-        <v>1.55</v>
-      </c>
       <c r="AG6">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH6">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AI6">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AJ6" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="AK6" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL6">
-        <v>1.2</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>1.7</v>
-      </c>
-      <c r="AO6">
-        <v>-1</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>1.57</v>
-      </c>
-      <c r="BC6">
-        <v>2.38</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>78</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45841.83333333334</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45841</v>
       </c>
       <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" t="s">
         <v>60</v>
       </c>
-      <c r="C7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E7" t="s">
-        <v>78</v>
-      </c>
       <c r="F7" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="L7">
         <v>1.58</v>
@@ -1792,111 +1459,57 @@
         <v>1.15</v>
       </c>
       <c r="AJ7" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="AK7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL7">
-        <v>1.17</v>
-      </c>
-      <c r="AM7">
-        <v>1.22</v>
-      </c>
-      <c r="AN7">
-        <v>2.4</v>
-      </c>
-      <c r="AO7">
-        <v>-1</v>
-      </c>
-      <c r="AP7">
-        <v>1.22</v>
-      </c>
-      <c r="AQ7">
-        <v>1.4</v>
-      </c>
-      <c r="AR7">
-        <v>1.65</v>
-      </c>
-      <c r="AS7">
-        <v>2</v>
-      </c>
-      <c r="AT7">
-        <v>2.55</v>
-      </c>
-      <c r="AU7">
-        <v>3.7</v>
-      </c>
-      <c r="AV7">
-        <v>2.7</v>
-      </c>
-      <c r="AW7">
-        <v>2.08</v>
-      </c>
-      <c r="AX7">
-        <v>1.71</v>
-      </c>
-      <c r="AY7">
-        <v>1.44</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>1.48</v>
-      </c>
-      <c r="BC7">
-        <v>3</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>78</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45841.85416666666</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45841</v>
       </c>
       <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" t="s">
         <v>61</v>
       </c>
-      <c r="C8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" t="s">
-        <v>79</v>
-      </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="L8">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="M8">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N8">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="O8">
         <v>1.67</v>
@@ -1908,165 +1521,111 @@
         <v>2.65</v>
       </c>
       <c r="R8">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="S8">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="T8">
-        <v>3.33</v>
+        <v>3.22</v>
       </c>
       <c r="U8">
         <v>1.3</v>
       </c>
       <c r="V8">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
         <v>1.07</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z8">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AA8">
         <v>2.9</v>
       </c>
       <c r="AB8">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="AC8">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AD8">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AE8">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF8">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG8">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AH8">
-        <v>7.8</v>
+        <v>7.75</v>
       </c>
       <c r="AI8">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AJ8" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AK8" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL8">
-        <v>1.33</v>
-      </c>
-      <c r="AM8">
-        <v>1.25</v>
-      </c>
-      <c r="AN8">
-        <v>1.85</v>
-      </c>
-      <c r="AO8">
-        <v>-1</v>
-      </c>
-      <c r="AP8">
-        <v>1.2</v>
-      </c>
-      <c r="AQ8">
-        <v>1.29</v>
-      </c>
-      <c r="AR8">
-        <v>1.57</v>
-      </c>
-      <c r="AS8">
-        <v>1.91</v>
-      </c>
-      <c r="AT8">
-        <v>2.4</v>
-      </c>
-      <c r="AU8">
-        <v>4</v>
-      </c>
-      <c r="AV8">
-        <v>3</v>
-      </c>
-      <c r="AW8">
-        <v>2.25</v>
-      </c>
-      <c r="AX8">
-        <v>1.8</v>
-      </c>
-      <c r="AY8">
-        <v>1.5</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>1.67</v>
-      </c>
-      <c r="BC8">
-        <v>2.65</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>88</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45841.89930555555</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45841</v>
       </c>
       <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" t="s">
         <v>62</v>
       </c>
-      <c r="C9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>72</v>
       </c>
-      <c r="E9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F9" t="s">
-        <v>90</v>
-      </c>
       <c r="G9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="L9">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="M9">
-        <v>4.01</v>
+        <v>3.8</v>
       </c>
       <c r="N9">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="O9">
         <v>1.67</v>
@@ -2081,153 +1640,99 @@
         <v>1.22</v>
       </c>
       <c r="S9">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="T9">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="U9">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V9">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="W9">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z9">
         <v>1.11</v>
       </c>
       <c r="AA9">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AB9">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AC9">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD9">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AE9">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AF9">
         <v>1.38</v>
       </c>
       <c r="AG9">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AH9">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="AI9">
         <v>1.3</v>
       </c>
       <c r="AJ9" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AK9" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL9">
-        <v>1.22</v>
-      </c>
-      <c r="AM9">
-        <v>0</v>
-      </c>
-      <c r="AN9">
-        <v>1.44</v>
-      </c>
-      <c r="AO9">
-        <v>-1</v>
-      </c>
-      <c r="AP9">
-        <v>0</v>
-      </c>
-      <c r="AQ9">
-        <v>0</v>
-      </c>
-      <c r="AR9">
-        <v>0</v>
-      </c>
-      <c r="AS9">
-        <v>0</v>
-      </c>
-      <c r="AT9">
-        <v>0</v>
-      </c>
-      <c r="AU9">
-        <v>0</v>
-      </c>
-      <c r="AV9">
-        <v>0</v>
-      </c>
-      <c r="AW9">
-        <v>0</v>
-      </c>
-      <c r="AX9">
-        <v>0</v>
-      </c>
-      <c r="AY9">
-        <v>0</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>1.67</v>
-      </c>
-      <c r="BC9">
-        <v>2.1</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>89</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45841.90625</v>
       </c>
     </row>
-    <row r="10" spans="1:56">
+    <row r="10" spans="1:38">
       <c r="A10" s="2">
         <v>45841</v>
       </c>
       <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" t="s">
         <v>63</v>
       </c>
-      <c r="C10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" t="s">
-        <v>81</v>
-      </c>
       <c r="F10" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -2248,22 +1753,22 @@
         <v>2.2</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T10">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="U10">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X10">
         <v>0</v>
@@ -2272,266 +1777,158 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB10">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AC10">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="AD10">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AE10">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AF10">
         <v>1.35</v>
       </c>
       <c r="AG10">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="AH10">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="AI10">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AJ10" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AK10" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL10">
-        <v>1.2</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-      <c r="AN10">
-        <v>1.52</v>
-      </c>
-      <c r="AO10">
-        <v>-1</v>
-      </c>
-      <c r="AP10">
-        <v>0</v>
-      </c>
-      <c r="AQ10">
-        <v>0</v>
-      </c>
-      <c r="AR10">
-        <v>0</v>
-      </c>
-      <c r="AS10">
-        <v>0</v>
-      </c>
-      <c r="AT10">
-        <v>0</v>
-      </c>
-      <c r="AU10">
-        <v>0</v>
-      </c>
-      <c r="AV10">
-        <v>0</v>
-      </c>
-      <c r="AW10">
-        <v>0</v>
-      </c>
-      <c r="AX10">
-        <v>0</v>
-      </c>
-      <c r="AY10">
-        <v>0</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>1.62</v>
-      </c>
-      <c r="BC10">
-        <v>2.2</v>
-      </c>
-      <c r="BD10" s="3">
+        <v>90</v>
+      </c>
+      <c r="AL10" s="3">
         <v>45841.95833333334</v>
       </c>
     </row>
-    <row r="11" spans="1:56">
+    <row r="11" spans="1:38">
       <c r="A11" s="2">
         <v>45841</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="F11" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R11">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S11">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="T11">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="U11">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="V11">
-        <v>3.8</v>
+        <v>4.35</v>
       </c>
       <c r="W11">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z11">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AA11">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="AB11">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AC11">
+        <v>2.75</v>
+      </c>
+      <c r="AD11">
+        <v>1.9</v>
+      </c>
+      <c r="AE11">
+        <v>1.72</v>
+      </c>
+      <c r="AF11">
+        <v>1.47</v>
+      </c>
+      <c r="AG11">
+        <v>2.4</v>
+      </c>
+      <c r="AH11">
         <v>3.2</v>
       </c>
-      <c r="AD11">
-        <v>1.83</v>
-      </c>
-      <c r="AE11">
-        <v>1.91</v>
-      </c>
-      <c r="AF11">
-        <v>1.48</v>
-      </c>
-      <c r="AG11">
-        <v>2.54</v>
-      </c>
-      <c r="AH11">
-        <v>2.8</v>
-      </c>
       <c r="AI11">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AJ11" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AK11" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL11">
-        <v>1.17</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>2.75</v>
-      </c>
-      <c r="AO11">
-        <v>-1</v>
-      </c>
-      <c r="AP11">
-        <v>0</v>
-      </c>
-      <c r="AQ11">
-        <v>0</v>
-      </c>
-      <c r="AR11">
-        <v>0</v>
-      </c>
-      <c r="AS11">
-        <v>0</v>
-      </c>
-      <c r="AT11">
-        <v>0</v>
-      </c>
-      <c r="AU11">
-        <v>0</v>
-      </c>
-      <c r="AV11">
-        <v>0</v>
-      </c>
-      <c r="AW11">
-        <v>0</v>
-      </c>
-      <c r="AX11">
-        <v>0</v>
-      </c>
-      <c r="AY11">
-        <v>0</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>0</v>
-      </c>
-      <c r="BC11">
-        <v>0</v>
-      </c>
-      <c r="BD11" s="3">
+        <v>91</v>
+      </c>
+      <c r="AL11" s="3">
         <v>45841.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-07-03.xlsx
+++ b/jogos_2025-07-03.xlsx
@@ -652,30 +652,30 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -702,16 +702,16 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -727,7 +727,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12', '18']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1300,7 +1300,7 @@
         <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="M7" t="n">
-        <v>3.73</v>
+        <v>4.1</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="O7" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="P7" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.86</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['20', '49', '74']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
         <v>1.22</v>
       </c>
-      <c r="X7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>['20', '49', '74']</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH7" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45841.85416666666</v>
